--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_14-04-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_14-04-2026.xlsx
@@ -518,12 +518,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£12.76</t>
+          <t>£12.33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.51</t>
+          <t>£14.06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>Cloudflare Blocked</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -657,17 +657,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£18.51</t>
+          <t>£18.33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£19.23</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.92</t>
+          <t>£18.44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£20.83</t>
+          <t>£22.91</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£25.56</t>
+          <t>£28.12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£28.78</t>
+          <t>£31.66</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£29.96</t>
+          <t>£32.96</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£32.09</t>
+          <t>£35.30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£35.74</t>
+          <t>£39.31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£38.02</t>
+          <t>£41.82</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>£42.53</t>
+          <t>£46.78</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1305,17 +1305,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.49</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£46.10</t>
+          <t>£50.71</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£49.75</t>
+          <t>£47.85</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£53.19</t>
+          <t>£58.51</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£49.76</t>
+          <t>£49.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£55.23</t>
+          <t>£60.75</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>£55.61</t>
+          <t>£61.17</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
